--- a/output/pdf_financials_xlsx/TAI.xlsx
+++ b/output/pdf_financials_xlsx/TAI.xlsx
@@ -2084,13 +2084,13 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0</v>
+        <v>0.203661</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>0.286178</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>0.07115200000000001</v>
       </c>
     </row>
     <row r="93">
@@ -3064,7 +3064,11 @@
           <t>Share-based payment reserve 8</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr"/>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E9" t="inlineStr">
         <is>
           <t>-</t>
@@ -3093,7 +3097,11 @@
           <t>Warrant reserve 7</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr"/>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E10" t="inlineStr">
         <is>
           <t>-</t>
@@ -3509,7 +3517,11 @@
           <t>Share-based payment reserve 8</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr"/>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E24" s="5" t="n">
         <v>0.122061</v>
       </c>
@@ -3538,7 +3550,11 @@
           <t>Warrant reserve 7</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr"/>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E25" s="5" t="n">
         <v>0.08160000000000001</v>
       </c>

--- a/output/pdf_financials_xlsx/TAI.xlsx
+++ b/output/pdf_financials_xlsx/TAI.xlsx
@@ -1120,13 +1120,13 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.06696199999999999</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.061884</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.030137</v>
       </c>
     </row>
     <row r="35">
@@ -1152,13 +1152,13 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.06696199999999999</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.061884</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.030137</v>
       </c>
     </row>
     <row r="37">
@@ -2880,7 +2880,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E3" s="5" t="n">

--- a/output/pdf_financials_xlsx/TAI.xlsx
+++ b/output/pdf_financials_xlsx/TAI.xlsx
@@ -4044,7 +4044,11 @@
           <t>Private Placement 7</t>
         </is>
       </c>
-      <c r="D41" t="inlineStr"/>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E41" s="5" t="n">
         <v>0.2635</v>
       </c>
